--- a/docs/BETA_TESTERS.xlsx
+++ b/docs/BETA_TESTERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denni\PycharmProjects\Kira\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0474B8-3541-4541-B77D-471BCE068CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0328EA0-9DDB-4F53-A0C5-743EA24291F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="239">
   <si>
     <t>User_type</t>
   </si>
@@ -235,27 +235,12 @@
     <t>YES</t>
   </si>
   <si>
-    <t>Needs nudge</t>
-  </si>
-  <si>
-    <t>Dennis</t>
-  </si>
-  <si>
-    <t>Corporate</t>
-  </si>
-  <si>
     <t>CorporateAI Solutions</t>
   </si>
   <si>
     <t>61402612471</t>
   </si>
   <si>
-    <t>dennis@factory2key.com.au</t>
-  </si>
-  <si>
-    <t>F2K</t>
-  </si>
-  <si>
     <t>Factory2key</t>
   </si>
   <si>
@@ -283,9 +268,6 @@
     <t>Haque</t>
   </si>
   <si>
-    <t>US</t>
-  </si>
-  <si>
     <t>hardiktech66@gmail.com</t>
   </si>
   <si>
@@ -388,12 +370,6 @@
     <t>Muhasi</t>
   </si>
   <si>
-    <t>mcmdennis@gmail.com</t>
-  </si>
-  <si>
-    <t>McMahon</t>
-  </si>
-  <si>
     <t>Global Buildtech</t>
   </si>
   <si>
@@ -430,9 +406,6 @@
     <t>Neil</t>
   </si>
   <si>
-    <t>Mulchay</t>
-  </si>
-  <si>
     <t>paul@presencegraph.co.nz</t>
   </si>
   <si>
@@ -595,9 +568,6 @@
     <t>Brennan</t>
   </si>
   <si>
-    <t>Name supplied 2026-09-06 (Will Brennan).</t>
-  </si>
-  <si>
     <t>tim.eckenfels@thealternativeboard.com.au</t>
   </si>
   <si>
@@ -641,14 +611,156 @@
   </si>
   <si>
     <t>O'Neill</t>
+  </si>
+  <si>
+    <t>Advisory Partner</t>
+  </si>
+  <si>
+    <t>Ron</t>
+  </si>
+  <si>
+    <t>D'Vari</t>
+  </si>
+  <si>
+    <t>rdvari@newoak.com</t>
+  </si>
+  <si>
+    <t>Special Treatment Needed</t>
+  </si>
+  <si>
+    <t>Why Special Treatment</t>
+  </si>
+  <si>
+    <t>Met Darren, mentioned Kira but he hasn't seen anything oif her yet. Did discuss the BBBO scenario</t>
+  </si>
+  <si>
+    <t>Spoke to Zhai, mentioned Kira but he hasn't seen anything of her yet. Did discuss the BBBO scenario</t>
+  </si>
+  <si>
+    <t>Long term relationship already, need to bring up to speed</t>
+  </si>
+  <si>
+    <t>Had zoom meetign with Lisa and Tom and Richard from Boomi, want to share the vision with Lisa so we start talking integration and leverging boomi's own client list, not just being a supplier of services to Kira</t>
+  </si>
+  <si>
+    <t>Said I would share both the Kira beta testing and the github repos for their tech review and feedback (Shani and Yuvraj and Darshilp have already experienced the old beta testing, so this is the new updated version of Kira and they will need background)</t>
+  </si>
+  <si>
+    <t>PAK</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>VIETNAM</t>
+  </si>
+  <si>
+    <t>mcmdennis+bree@gmail.com</t>
+  </si>
+  <si>
+    <t>Bree</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>dennis+shaz@corporateaisolutions.com</t>
+  </si>
+  <si>
+    <t>Shaz</t>
+  </si>
+  <si>
+    <t>dennis+garry@factory2key.com.au</t>
+  </si>
+  <si>
+    <t>Garry</t>
+  </si>
+  <si>
+    <t>Called, spoke to, Ash to check emaisl and come back to me on possible collaboration</t>
+  </si>
+  <si>
+    <t>Left message for Sukhdeep</t>
+  </si>
+  <si>
+    <t>Left message for Tom</t>
+  </si>
+  <si>
+    <t>Left message for Tim</t>
+  </si>
+  <si>
+    <t>No phone so only emails but work in conjunction with Darren Cron</t>
+  </si>
+  <si>
+    <t>Spoke to Simon, advised re rebuild and repositioning, asked him to review the emails and get back to me. He said he would so in a couple of days</t>
+  </si>
+  <si>
+    <t>Sent whatsapp message to brian</t>
+  </si>
+  <si>
+    <t>Left message for Darren</t>
+  </si>
+  <si>
+    <t>Left message for Zhai</t>
+  </si>
+  <si>
+    <t>Left message for Josh</t>
+  </si>
+  <si>
+    <t>No phone so only emails</t>
+  </si>
+  <si>
+    <t>Mulcahy</t>
+  </si>
+  <si>
+    <t>Left message for james</t>
+  </si>
+  <si>
+    <t>Left message for neiul re Craig etc</t>
+  </si>
+  <si>
+    <t>g.douglas.moffatt@gmail.com</t>
+  </si>
+  <si>
+    <t>Graham</t>
+  </si>
+  <si>
+    <t>Moffatt</t>
+  </si>
+  <si>
+    <t>Graham was my Nominee Supervisor for what was NatureZen Constructions Qld before it got deregistered but he aslo has his own building company that puts him in the BBBO space so effectively he's a feedback Partner</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -673,16 +785,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1020,71 +1140,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultColWidth="78.08203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.4140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.9140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.9140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="36" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="78.08203125" style="1"/>
+    <col min="5" max="5" width="13.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="6.75" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="17.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="5.9140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="29.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="29.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="36" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="78.08203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,341 +1241,365 @@
         <v>18</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
+      <c r="H3" s="1">
+        <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="1">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="L5" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="L8" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>17</v>
@@ -1462,168 +1614,180 @@
         <v>3</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>17</v>
+      <c r="H11" s="1">
+        <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="1">
-        <v>2</v>
+      <c r="H12" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>17</v>
@@ -1634,61 +1798,64 @@
       <c r="G14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>17</v>
+      <c r="H14" s="1">
+        <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>44</v>
+        <v>209</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="1">
-        <v>1</v>
+      <c r="H15" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>70</v>
@@ -1697,42 +1864,45 @@
         <v>21</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="H16" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>70</v>
@@ -1741,71 +1911,77 @@
         <v>21</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="31" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="1">
-        <v>1</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>17</v>
@@ -1829,461 +2005,476 @@
         <v>21</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="124" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H19" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>87</v>
+        <v>209</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="124" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H20" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="124" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>94</v>
+        <v>209</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="31" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="1">
+        <v>3</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="L24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="1">
         <v>3</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="1" t="s">
+      <c r="I26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="1">
+      <c r="L26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="1">
         <v>1</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J24" s="1" t="s">
+      <c r="I27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" s="1">
-        <v>2</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="1" t="s">
+      <c r="L27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" s="1">
-        <v>3</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="K28" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>17</v>
@@ -2298,124 +2489,133 @@
         <v>3</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="H30" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="L31" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>17</v>
@@ -2426,161 +2626,167 @@
       <c r="G32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="1">
         <v>3</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" s="1" t="s">
+      <c r="I34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H33" s="1">
-        <v>2</v>
-      </c>
-      <c r="I33" s="1" t="s">
+      <c r="L34" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="1" t="s">
+      <c r="E35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="1">
-        <v>2</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="K35" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>14</v>
       </c>
@@ -2588,11 +2794,11 @@
         <v>140</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="E36" s="1" t="s">
         <v>17</v>
       </c>
@@ -2606,212 +2812,224 @@
         <v>17</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="J36" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="1">
+        <v>3</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="K38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="1">
-        <v>2</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="D41" s="1" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>17</v>
@@ -2822,40 +3040,46 @@
       <c r="G41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H41" s="1">
-        <v>3</v>
+      <c r="H41" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>17</v>
@@ -2870,86 +3094,92 @@
         <v>17</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>17</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>160</v>
+        <v>52</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H43" s="1">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>17</v>
@@ -2958,101 +3188,107 @@
         <v>1</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>40</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>169</v>
+        <v>92</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>168</v>
+        <v>93</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>171</v>
+        <v>17</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H45" s="1">
-        <v>1</v>
+      <c r="H45" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>176</v>
+        <v>17</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H46" s="1">
-        <v>1</v>
+      <c r="H46" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>70</v>
@@ -3061,21 +3297,24 @@
         <v>21</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>17</v>
@@ -3090,7 +3329,7 @@
         <v>17</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>44</v>
@@ -3099,39 +3338,42 @@
         <v>17</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>183</v>
+        <v>17</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H48" s="1">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>64</v>
@@ -3140,74 +3382,80 @@
         <v>44</v>
       </c>
       <c r="K48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="62" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="L49" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="31" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>17</v>
@@ -3222,248 +3470,347 @@
         <v>17</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>17</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>17</v>
+        <v>174</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>17</v>
+        <v>175</v>
+      </c>
+      <c r="H51" s="1">
+        <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H52" s="1">
-        <v>3</v>
+      <c r="H52" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="1">
+        <v>2</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H53" s="1">
-        <v>3</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H54" s="1">
-        <v>1</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="1" t="s">
+      <c r="E56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>17</v>
+      <c r="K56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="124" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P56">
+    <sortCondition descending="1" ref="I2:I56"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="B31" r:id="rId1" xr:uid="{BBCFDB3A-21A4-42A1-AED5-62E99AB96B7A}"/>
+    <hyperlink ref="B27" r:id="rId2" xr:uid="{EB8DF5FC-D288-40C4-A971-87056F0C0DD7}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{7658C1DC-9207-4A08-9A8C-709F51020400}"/>
+    <hyperlink ref="B57" r:id="rId4" xr:uid="{E578F826-B2D1-4C8B-9A66-40C1F9739D9B}"/>
+    <hyperlink ref="M57" r:id="rId5" xr:uid="{E28585C7-6D2E-4199-98F1-E2E55A633C26}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId6"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N55" numberStoredAsText="1"/>
+    <ignoredError sqref="P1 A1:M1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>